--- a/data/availability/projects/pre-developments/the-brooks.xlsx
+++ b/data/availability/projects/pre-developments/the-brooks.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1059,7 +1059,6 @@
       <c r="G2" t="n">
         <v>145</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1116,7 +1115,6 @@
       <c r="G3" t="n">
         <v>157</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1173,7 +1171,6 @@
       <c r="G4" t="n">
         <v>176</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1230,7 +1227,6 @@
       <c r="G5" t="n">
         <v>194</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1287,7 +1283,6 @@
       <c r="G6" t="n">
         <v>227</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1344,7 +1339,6 @@
       <c r="G7" t="n">
         <v>126</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1355,7 +1349,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1401,7 +1395,6 @@
       <c r="G8" t="n">
         <v>145</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1412,7 +1405,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1458,7 +1451,6 @@
       <c r="G9" t="n">
         <v>216</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1469,7 +1461,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1515,7 +1507,6 @@
       <c r="G10" t="n">
         <v>251</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1526,7 +1517,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1572,7 +1563,6 @@
       <c r="G11" t="n">
         <v>249</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1583,7 +1573,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1629,7 +1619,6 @@
       <c r="G12" t="n">
         <v>266</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1640,7 +1629,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1686,7 +1675,6 @@
       <c r="G13" t="n">
         <v>304</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1697,7 +1685,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
